--- a/src/test/resources/testdata/Modules/01_Login/CompanyLogin/01_CompanyLoginTest.xlsx
+++ b/src/test/resources/testdata/Modules/01_Login/CompanyLogin/01_CompanyLoginTest.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\testing\Documents\Bandhan_World_APPIUM\src\test\resources\testdata\Modules\01_Login\CompanyLogin\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B83BA64B-0F43-4B33-9EE1-F12C2E638364}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EADD90E-5EEF-4DB4-8BDD-8CAE86D91395}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{D5674106-8292-4F40-9DFC-E6EAC771FC2F}"/>
   </bookViews>
@@ -70,9 +70,6 @@
     <t>MODULE_NAME</t>
   </si>
   <si>
-    <t>2601000018</t>
-  </si>
-  <si>
     <t>clickonwarningdialogbox
 connectwifi
 entercompanyname
@@ -103,6 +100,9 @@
   </si>
   <si>
     <t>01_CompanyLogin</t>
+  </si>
+  <si>
+    <t>2602000005</t>
   </si>
 </sst>
 </file>
@@ -644,7 +644,7 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyBorder="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -655,6 +655,9 @@
     <xf numFmtId="49" fontId="13" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="13" fillId="33" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="13" fillId="33" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1072,11 +1075,11 @@
       </c>
     </row>
     <row r="2" spans="1:8" ht="87" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
-        <v>16</v>
+      <c r="A2" s="8" t="s">
+        <v>23</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>6</v>
@@ -1085,22 +1088,22 @@
         <v>4</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F2" s="3"/>
       <c r="G2" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="58" x14ac:dyDescent="0.35">
-      <c r="A3" s="1" t="s">
-        <v>16</v>
+      <c r="A3" s="8" t="s">
+        <v>23</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>7</v>
@@ -1109,24 +1112,24 @@
         <v>5</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="58" x14ac:dyDescent="0.35">
-      <c r="A4" s="1" t="s">
-        <v>16</v>
+      <c r="A4" s="8" t="s">
+        <v>23</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>8</v>
@@ -1135,10 +1138,10 @@
         <v>9</v>
       </c>
       <c r="E4" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>22</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>10</v>

--- a/src/test/resources/testdata/Modules/01_Login/CompanyLogin/01_CompanyLoginTest.xlsx
+++ b/src/test/resources/testdata/Modules/01_Login/CompanyLogin/01_CompanyLoginTest.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\testing\Documents\Bandhan_World_APPIUM\src\test\resources\testdata\Modules\01_Login\CompanyLogin\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EADD90E-5EEF-4DB4-8BDD-8CAE86D91395}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B819941-7541-4D78-9681-5BDAE21A6AF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{D5674106-8292-4F40-9DFC-E6EAC771FC2F}"/>
   </bookViews>
@@ -90,19 +90,20 @@
 verifycompanyerrormessage</t>
   </si>
   <si>
+    <t>bandhaninftest</t>
+  </si>
+  <si>
+    <t>01_CompanyLogin</t>
+  </si>
+  <si>
+    <t>2602000005</t>
+  </si>
+  <si>
     <t>entercompanyname
 clicksubmitbutton
 hidekeyboard
+relaunchapp
 verifychooselanguagepagedisplay</t>
-  </si>
-  <si>
-    <t>bandhaninftest</t>
-  </si>
-  <si>
-    <t>01_CompanyLogin</t>
-  </si>
-  <si>
-    <t>2602000005</t>
   </si>
 </sst>
 </file>
@@ -1076,10 +1077,10 @@
     </row>
     <row r="2" spans="1:8" ht="87" x14ac:dyDescent="0.35">
       <c r="A2" s="8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>6</v>
@@ -1100,10 +1101,10 @@
     </row>
     <row r="3" spans="1:8" ht="58" x14ac:dyDescent="0.35">
       <c r="A3" s="8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>7</v>
@@ -1124,12 +1125,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="58" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A4" s="8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>8</v>
@@ -1138,10 +1139,10 @@
         <v>9</v>
       </c>
       <c r="E4" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>21</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>10</v>
